--- a/metrics_mean.xlsx
+++ b/metrics_mean.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,346 +478,6 @@
         <is>
           <t>F1 score</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AdaBoost</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.6903423761305365</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.6900232260948062</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.6906615261662669</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.8936087295401403</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.006259457972210758</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.9998188704100115</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.8053097345132744</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.8936821577068845</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.0124223602484472</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.6547323622232979</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.6544915094433224</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.6549732150032734</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.8931013691377815</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.8931013691377815</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>GradientBoosting</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.6964413301778878</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.6960733016333774</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6968093587223981</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8939616759069986</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.01341312422616591</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.999357813271859</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.8943230797568613</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.02633178043346162</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GaussianNB</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.5963122315401529</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.5961331083262569</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.5964913547540489</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.8930866630391623</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0001375705048837529</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.9999670673472748</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8931113594917348</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.000275027502750275</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>LinearDiscriminantAnalysis</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.6161033304000212</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.6148192663957489</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.6173873944042935</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.8371814291386638</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1473380107304994</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.9197513584719249</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.1801665404996215</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.900120055757439</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.1621069360880917</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>LightGBM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.6787635095402416</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.6785153233026227</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.6790116957778605</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8931013691377815</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.8931013691377815</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6858994536527733</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.6854787227238374</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.6863201845817092</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.8937999088221885</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.01857201815930664</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.9985591964432735</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6067415730337079</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.8947422779281905</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.0360408462924648</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MultilayerPerceptron</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5272133209522144</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.5254574221874445</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5289692197169843</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8056956719951764</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1745081854450406</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8812448542730117</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.1495784446671777</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.8991826070885522</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.1610844788723451</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.6453269654816732</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.6449211172120278</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.6457328137513186</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.8932999014691393</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.002476269087907552</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.9999259015313684</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.8933307834325097</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.004937255708701913</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.6607341481820318</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.660435705716977</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.6610325906470866</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.8929837203488287</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0008254230293025176</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.9997694714309238</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.8931581812030186</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.00164631636712855</v>
       </c>
     </row>
   </sheetData>
